--- a/files/九龙-启德-Monaco 第1期.xlsx
+++ b/files/九龙-启德-Monaco 第1期.xlsx
@@ -6319,7 +6319,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -20285,7 +20285,7 @@
           <t>C | 551呎 (3房)
 $1,353万
 $24,555/呎
-(25年-11月)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
@@ -21779,7 +21779,7 @@
           <t>B | 480呎 (2房)
 $1,274万
 $26,544/呎
-(26年-03月)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -22811,7 +22811,7 @@
           <t>E | 445呎 (2房)
 $1,040万
 $23,360/呎
-(25年-12月)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">

--- a/files/九龙-启德-Monaco 第1期.xlsx
+++ b/files/九龙-启德-Monaco 第1期.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +45,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -64,7 +69,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -75,7 +80,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -86,7 +91,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -96,9 +101,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -146,8 +172,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,19 +220,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,13 +238,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -19045,166 +19083,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco 第1期 - 2A座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>185 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>184 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1394呎 (4+房)
-$4,928万
+$4928万
 $35,352/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 552呎 (3房)
-$1,454万
+$1454万
 $26,333/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 470呎 (2房)
-$1,261万
+$1261万
 $26,838/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,794万
+$1794万
 $26,610/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $908万
@@ -19213,53 +19251,53 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$2,120万
+$2120万
 $27,822/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,896万
+$1896万
 $27,972/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,562万
+$1562万
 $28,347/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,242万
+$1242万
 $25,776/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,708万
+$1708万
 $25,337/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $908万
@@ -19268,53 +19306,53 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,954万
+$1954万
 $25,640/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,800万
+$1800万
 $26,541/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,467万
+$1467万
 $26,628/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,258万
+$1258万
 $26,089/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,761万
+$1761万
 $26,122/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $908万
@@ -19323,21 +19361,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$2,001万
+$2001万
 $26,260/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
 招标单位
@@ -19345,31 +19383,31 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,427万
+$1427万
 $25,897/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,281万
+$1281万
 $26,575/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,772万
+$1772万
 $26,294/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $903万
@@ -19378,53 +19416,53 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$2,082万
+$2082万
 $27,323/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,958万
+$1958万
 $28,873/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,424万
+$1424万
 $25,835/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,281万
+$1281万
 $26,577/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,767万
+$1767万
 $26,212/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $903万
@@ -19433,53 +19471,53 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,966万
+$1966万
 $25,801/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,872万
+$1872万
 $27,611/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,490万
+$1490万
 $27,038/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,301万
+$1301万
 $26,992/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,687万
+$1687万
 $25,036/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $906万
@@ -19488,53 +19526,53 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,944万
+$1944万
 $25,509/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,861万
+$1861万
 $27,448/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,485万
+$1485万
 $26,956/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,278万
+$1278万
 $26,510/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,722万
+$1722万
 $25,552/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $867万
@@ -19543,53 +19581,53 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,958万
+$1958万
 $25,729/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,861万
+$1861万
 $27,445/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,406万
+$1406万
 $25,523/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,220万
+$1220万
 $25,315/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,657万
+$1657万
 $24,586/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $866万
@@ -19598,53 +19636,53 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,928万
+$1928万
 $25,300/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,855万
+$1855万
 $27,363/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,442万
+$1442万
 $26,174/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,217万
+$1217万
 $25,241/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,750万
+$1750万
 $25,970/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $860万
@@ -19653,53 +19691,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$2,024万
+$2024万
 $26,603/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,906万
+$1906万
 $28,108/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,377万
+$1377万
 $24,995/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,248万
+$1248万
 $25,884/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,741万
+$1741万
 $25,826/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $859万
@@ -19708,53 +19746,53 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,889万
+$1889万
 $24,819/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,876万
+$1876万
 $27,662/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,429万
+$1429万
 $25,940/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,188万
+$1188万
 $24,656/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,658万
+$1658万
 $24,598/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $898万
@@ -19763,53 +19801,53 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,989万
+$1989万
 $26,137/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,838万
+$1838万
 $27,106/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,358万
+$1358万
 $24,648/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,237万
+$1237万
 $25,664/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,704万
+$1704万
 $25,286/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $859万
@@ -19818,53 +19856,53 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,960万
+$1960万
 $25,757/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,932万
+$1932万
 $28,497/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,361万
+$1361万
 $24,699/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,181万
+$1181万
 $24,508/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,623万
+$1623万
 $24,086/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $889万
@@ -19873,53 +19911,53 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,990万
+$1990万
 $26,109/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,822万
+$1822万
 $26,876/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,416万
+$1416万
 $25,708/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,230万
+$1230万
 $25,510/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,647万
+$1647万
 $24,432/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $850万
@@ -19928,53 +19966,53 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,902万
+$1902万
 $24,961/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,795万
+$1795万
 $26,479/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,412万
+$1412万
 $25,632/呎
 (21年-02月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,226万
+$1226万
 $25,436/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,710万
+$1710万
 $25,366/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $849万
@@ -19983,53 +20021,53 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,861万
+$1861万
 $24,451/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,811万
+$1811万
 $26,715/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,374万
+$1374万
 $24,938/呎
 (21年-02月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,196万
+$1196万
 $24,822/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,680万
+$1680万
 $24,921/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $848万
@@ -20038,53 +20076,53 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,855万
+$1855万
 $24,345/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,806万
+$1806万
 $26,636/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,393万
+$1393万
 $25,285/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,192万
+$1192万
 $24,739/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,604万
+$1604万
 $23,798/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 353呎 (1房)
 $882万
@@ -20093,53 +20131,53 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,850万
+$1850万
 $24,304/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,737万
+$1737万
 $25,614/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,406万
+$1406万
 $25,514/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,219万
+$1219万
 $25,297/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,599万
+$1599万
 $23,728/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $881万
@@ -20148,53 +20186,53 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,991万
+$1991万
 $26,127/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,710万
+$1710万
 $25,224/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,385万
+$1385万
 $25,134/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,164万
+$1164万
 $24,160/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,618万
+$1618万
 $24,006/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $837万
@@ -20203,37 +20241,37 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,865万
+$1865万
 $24,506/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,721万
+$1721万
 $25,385/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,385万
+$1385万
 $25,136/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
 $821万
@@ -20241,15 +20279,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,573万
+$1573万
 $23,341/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $832万
@@ -20258,53 +20296,53 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,765万
+$1765万
 $23,167/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,695万
+$1695万
 $24,999/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,353万
+$1353万
 $24,555/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,174万
+$1174万
 $24,365/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,568万
+$1568万
 $23,272/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $866万
@@ -20313,53 +20351,53 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,743万
+$1743万
 $22,899/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,763万
+$1763万
 $26,007/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,311万
+$1311万
 $23,789/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,154万
+$1154万
 $23,952/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,633万
+$1633万
 $24,224/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $864万
@@ -20368,53 +20406,53 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,737万
+$1737万
 $22,801/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,685万
+$1685万
 $24,850/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,323万
+$1323万
 $24,015/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,167万
+$1167万
 $24,210/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,559万
+$1559万
 $23,132/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $862万
@@ -20423,53 +20461,53 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,756万
+$1756万
 $23,076/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,700万
+$1700万
 $25,081/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,303万
+$1303万
 $23,646/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,192万
+$1192万
 $24,734/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,607万
+$1607万
 $23,849/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $859万
@@ -20478,53 +20516,53 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,762万
+$1762万
 $23,119/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,727万
+$1727万
 $25,468/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,356万
+$1356万
 $24,613/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,147万
+$1147万
 $23,797/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,574万
+$1574万
 $23,361/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $857万
@@ -20533,53 +20571,53 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,722万
+$1722万
 $22,597/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,752万
+$1752万
 $25,848/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,398万
+$1398万
 $25,367/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,144万
+$1144万
 $23,726/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,545万
+$1545万
 $22,924/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $858万
@@ -20588,53 +20626,53 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,783万
+$1783万
 $23,404/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,685万
+$1685万
 $24,855/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,311万
+$1311万
 $23,789/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,143万
+$1143万
 $23,714/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,540万
+$1540万
 $22,856/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $856万
@@ -20643,53 +20681,53 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,773万
+$1773万
 $23,296/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,732万
+$1732万
 $25,544/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,316万
+$1316万
 $23,882/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,177万
+$1177万
 $24,427/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,624万
+$1624万
 $24,098/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $807万
@@ -20698,53 +20736,53 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,693万
+$1693万
 $22,217/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,642万
+$1642万
 $24,215/呎
 (21年-05月)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,336万
+$1336万
 $24,247/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,124万
+$1124万
 $23,328/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,527万
+$1527万
 $22,653/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $794万
@@ -20753,53 +20791,53 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 761呎 (3房)
-$1,889万
+$1889万
 $24,820/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,718万
+$1718万
 $25,342/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,276万
+$1276万
 $23,156/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,121万
+$1121万
 $23,257/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,589万
+$1589万
 $23,580/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $815万
@@ -20808,53 +20846,53 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 762呎 (3房)
-$1,674万
+$1674万
 $21,975/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-$1,713万
+$1713万
 $25,265/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 551呎 (3房)
-$1,272万
+$1272万
 $23,085/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 482呎 (2房)
-$1,118万
+$1118万
 $23,189/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 674呎 (3房)
-$1,503万
+$1503万
 $22,295/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 354呎 (1房)
 $766万
@@ -20865,7 +20903,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -20878,155 +20916,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco 第1期 - 2B座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>214 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>213 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,927万
+$1927万
 $26,512/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,287万
+$1287万
 $26,810/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $902万
@@ -21034,23 +21072,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,149万
+$1149万
 $26,288/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,104万
+$1104万
 $24,809/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $719万
@@ -21058,38 +21096,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,087万
+$1087万
 $24,649/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,921万
+$1921万
 $26,421/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,315万
+$1315万
 $27,394/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $901万
@@ -21097,23 +21135,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,094万
+$1094万
 $25,027/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,098万
+$1098万
 $24,663/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $718万
@@ -21121,38 +21159,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,103万
+$1103万
 $25,018/呎
 (21年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,945万
+$1945万
 $26,757/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,330万
+$1330万
 $27,712/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $900万
@@ -21160,23 +21198,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,090万
+$1090万
 $24,954/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,166万
+$1166万
 $26,202/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $704万
@@ -21184,38 +21222,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,051万
+$1051万
 $23,830/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$2,006万
+$2006万
 $27,598/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,246万
+$1246万
 $25,952/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $938万
@@ -21223,23 +21261,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,093万
+$1093万
 $25,002/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,091万
+$1091万
 $24,515/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $674万
@@ -21247,38 +21285,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,071万
+$1071万
 $24,295/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$2,011万
+$2011万
 $27,667/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,265万
+$1265万
 $26,362/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $937万
@@ -21286,23 +21324,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,154万
+$1154万
 $26,407/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,088万
+$1088万
 $24,440/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $688万
@@ -21310,62 +21348,62 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,088万
+$1088万
 $24,667/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,982万
+$1982万
 $27,257/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,248万
+$1248万
 $25,992/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
-$1,128万
+$1128万
 $32,507/呎
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,097万
+$1097万
 $25,105/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,149万
+$1149万
 $25,813/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $707万
@@ -21373,38 +21411,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,039万
+$1039万
 $23,558/呎
 (21年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,940万
+$1940万
 $26,684/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,295万
+$1295万
 $26,985/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $935万
@@ -21412,23 +21450,23 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,078万
+$1078万
 $24,657/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,078万
+$1078万
 $24,234/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $717万
@@ -21436,38 +21474,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,094万
+$1094万
 $24,816/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,929万
+$1929万
 $26,536/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,234万
+$1234万
 $25,708/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $934万
@@ -21475,23 +21513,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,101万
+$1101万
 $25,201/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,102万
+$1102万
 $24,771/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $673万
@@ -21499,38 +21537,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,078万
+$1078万
 $24,447/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,900万
+$1900万
 $26,132/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,230万
+$1230万
 $25,631/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $932万
@@ -21538,23 +21576,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,093万
+$1093万
 $25,005/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,085万
+$1085万
 $24,391/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $691万
@@ -21562,38 +21600,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,030万
+$1030万
 $23,347/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,871万
+$1871万
 $25,730/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,410万
+$1410万
 $29,369/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $890万
@@ -21601,23 +21639,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,073万
+$1073万
 $24,556/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,116万
+$1116万
 $25,074/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $672万
@@ -21625,38 +21663,38 @@
 (21年-01月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,026万
+$1026万
 $23,277/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,883万
+$1883万
 $25,900/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,213万
+$1213万
 $25,273/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $924万
@@ -21664,23 +21702,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,088万
+$1088万
 $24,902/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,109万
+$1109万
 $24,926/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $709万
@@ -21688,38 +21726,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,015万
+$1015万
 $23,023/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,877万
+$1877万
 $25,821/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,210万
+$1210万
 $25,198/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $882万
@@ -21727,23 +21765,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,085万
+$1085万
 $24,826/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,073万
+$1073万
 $24,103/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $706万
@@ -21751,38 +21789,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,057万
+$1057万
 $23,964/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,877万
+$1877万
 $25,824/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,274万
+$1274万
 $26,544/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $900万
@@ -21790,23 +21828,23 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,087万
+$1087万
 $24,874/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,069万
+$1069万
 $24,029/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $695万
@@ -21814,38 +21852,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,009万
+$1009万
 $22,884/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,912万
+$1912万
 $26,304/呎
 (21年-05月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,202万
+$1202万
 $25,046/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $893万
@@ -21853,23 +21891,23 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,057万
+$1057万
 $24,192/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,099万
+$1099万
 $24,701/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $677万
@@ -21877,38 +21915,38 @@
 (21年-01月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,006万
+$1006万
 $22,816/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,837万
+$1837万
 $25,271/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,214万
+$1214万
 $25,285/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $861万
@@ -21916,23 +21954,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,054万
+$1054万
 $24,121/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,050万
+$1050万
 $23,591/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $663万
@@ -21940,38 +21978,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,028万
+$1028万
 $23,322/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,884万
+$1884万
 $25,916/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,185万
+$1185万
 $24,692/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $898万
@@ -21979,23 +22017,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,051万
+$1051万
 $24,048/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,093万
+$1093万
 $24,555/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $669万
@@ -22003,38 +22041,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,000万
+$1000万
 $22,680/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,826万
+$1826万
 $25,121/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,236万
+$1236万
 $25,758/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $859万
@@ -22042,23 +22080,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,095万
+$1095万
 $25,050/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,044万
+$1044万
 $23,449/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $667万
@@ -22066,38 +22104,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,041万
+$1041万
 $23,608/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,901万
+$1901万
 $26,149/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,240万
+$1240万
 $25,838/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $859万
@@ -22105,23 +22143,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,047万
+$1047万
 $23,952/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,055万
+$1055万
 $23,701/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $675万
@@ -22129,7 +22167,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $994万
@@ -22138,29 +22176,29 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,815万
+$1815万
 $24,971/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,184万
+$1184万
 $24,675/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $896万
@@ -22168,23 +22206,23 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,079万
+$1079万
 $24,696/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,058万
+$1058万
 $23,775/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $673万
@@ -22192,38 +22230,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,035万
+$1035万
 $23,467/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,888万
+$1888万
 $25,970/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,177万
+$1177万
 $24,527/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $896万
@@ -22231,23 +22269,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,028万
+$1028万
 $23,515/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,071万
+$1071万
 $24,070/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $669万
@@ -22255,7 +22293,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $998万
@@ -22264,29 +22302,29 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,878万
+$1878万
 $25,836/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,174万
+$1174万
 $24,454/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $858万
@@ -22294,23 +22332,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,070万
+$1070万
 $24,476/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,087万
+$1087万
 $24,429/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $668万
@@ -22318,7 +22356,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $985万
@@ -22327,29 +22365,29 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,794万
+$1794万
 $24,674/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,222万
+$1222万
 $25,454/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $858万
@@ -22357,23 +22395,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,041万
+$1041万
 $23,815/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,065万
+$1065万
 $23,926/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $666万
@@ -22381,7 +22419,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $982万
@@ -22390,29 +22428,29 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,834万
+$1834万
 $25,220/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,157万
+$1157万
 $24,108/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $858万
@@ -22420,23 +22458,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,018万
+$1018万
 $23,304/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,017万
+$1017万
 $22,847/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $636万
@@ -22444,38 +22482,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,000万
+$1000万
 $22,664/呎
 (25年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,833万
+$1833万
 $25,208/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,154万
+$1154万
 $24,035/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $896万
@@ -22483,23 +22521,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,055万
+$1055万
 $24,135/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,014万
+$1014万
 $22,780/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $662万
@@ -22507,7 +22545,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $999万
@@ -22516,29 +22554,29 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,856万
+$1856万
 $25,530/呎
 (21年-01月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,160万
+$1160万
 $24,162/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $896万
@@ -22546,23 +22584,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,052万
+$1052万
 $24,064/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,011万
+$1011万
 $22,712/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $660万
@@ -22570,7 +22608,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $999万
@@ -22579,29 +22617,29 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,723万
+$1723万
 $23,702/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,207万
+$1207万
 $25,150/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $895万
@@ -22609,23 +22647,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,027万
+$1027万
 $23,499/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,008万
+$1008万
 $22,643/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $658万
@@ -22633,7 +22671,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $957万
@@ -22642,29 +22680,29 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,767万
+$1767万
 $24,308/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,204万
+$1204万
 $25,075/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $894万
@@ -22672,23 +22710,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,051万
+$1051万
 $24,041/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,049万
+$1049万
 $23,569/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $628万
@@ -22696,38 +22734,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
-$1,017万
+$1017万
 $23,061/呎
 (24年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,779万
+$1779万
 $24,466/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,146万
+$1146万
 $23,875/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $890万
@@ -22735,23 +22773,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,008万
+$1008万
 $23,062/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,030万
+$1030万
 $23,148/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $620万
@@ -22759,7 +22797,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $998万
@@ -22768,29 +22806,29 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,773万
+$1773万
 $24,393/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,183万
+$1183万
 $24,646/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $888万
@@ -22798,7 +22836,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
 $992万
@@ -22806,15 +22844,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,040万
+$1040万
 $23,360/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $615万
@@ -22822,7 +22860,7 @@
 (21年-01月)</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $956万
@@ -22831,29 +22869,29 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 727呎 (3房)
-$1,698万
+$1698万
 $23,349/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 480呎 (2房)
-$1,180万
+$1180万
 $24,573/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 347呎 (1房)
 $888万
@@ -22861,23 +22899,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
-$1,020万
+$1020万
 $23,352/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,030万
+$1030万
 $23,148/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 280呎 (开放式)
 $637万
@@ -22885,7 +22923,7 @@
 (21年-01月)</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 441呎 (2房)
 $986万
@@ -22894,16 +22932,16 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr"/>
-      <c r="C36" s="17" t="inlineStr"/>
-      <c r="D36" s="17" t="inlineStr"/>
-      <c r="E36" s="16" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr"/>
+      <c r="C35" s="21" t="inlineStr"/>
+      <c r="D35" s="21" t="inlineStr"/>
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
 $989万
@@ -22911,15 +22949,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,035万
+$1035万
 $23,267/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (开放式)
 $597万
@@ -22927,7 +22965,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>G | 452呎 (2房)
 $959万
@@ -22938,7 +22976,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
